--- a/static/data/exports/Retro_DL_AE_2008.xlsx
+++ b/static/data/exports/Retro_DL_AE_2008.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_DL_AE_2008.xlsx
+++ b/static/data/exports/Retro_DL_AE_2008.xlsx
@@ -2205,20 +2205,20 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1495482</v>
+        <v>1495481</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lal Bahadur Singh</t>
+          <t>Deen Dayal Singh</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RMEP</t>
+          <t>ABHM</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16219</v>
+        <v>16218</v>
       </c>
       <c r="E29" t="n">
         <v>414</v>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Lal Bahadur Singh</t>
+          <t>Deen Dayal Singh</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>RMEP</t>
+          <t>ABHM</t>
         </is>
       </c>
       <c r="Q29" t="b">
@@ -2267,20 +2267,20 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1495481</v>
+        <v>1495482</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deen Dayal Singh</t>
+          <t>Lal Bahadur Singh</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ABHM</t>
+          <t>RMEP</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16218</v>
+        <v>16219</v>
       </c>
       <c r="E30" t="n">
         <v>414</v>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Deen Dayal Singh</t>
+          <t>Lal Bahadur Singh</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ABHM</t>
+          <t>RMEP</t>
         </is>
       </c>
       <c r="Q30" t="b">
@@ -14109,20 +14109,20 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1495674</v>
+        <v>1495673</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Sunil Tiwari</t>
+          <t>Jai Veer</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>MBP</t>
+          <t>RALP</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>16224</v>
+        <v>16240</v>
       </c>
       <c r="E221" t="n">
         <v>222</v>
@@ -14146,12 +14146,12 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Sunil Tiwari</t>
+          <t>Jai Veer</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>MBP</t>
+          <t>RALP</t>
         </is>
       </c>
       <c r="Q221" t="b">
@@ -14171,20 +14171,20 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1495673</v>
+        <v>1495674</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Jai Veer</t>
+          <t>Sunil Tiwari</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>RALP</t>
+          <t>MBP</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>16240</v>
+        <v>16224</v>
       </c>
       <c r="E222" t="n">
         <v>222</v>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Jai Veer</t>
+          <t>Sunil Tiwari</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>RALP</t>
+          <t>MBP</t>
         </is>
       </c>
       <c r="Q222" t="b">
@@ -18520,11 +18520,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>16243</v>
+        <v>16525</v>
       </c>
       <c r="E292" t="n">
         <v>1496</v>
@@ -26642,11 +26642,11 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>16243</v>
+        <v>16525</v>
       </c>
       <c r="E423" t="n">
         <v>553</v>
@@ -27873,11 +27873,11 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>1495895</v>
+        <v>1495896</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>O P Sharma</t>
+          <t>Mohamad Manjoor</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -27910,7 +27910,7 @@
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>O P Sharma</t>
+          <t>Mohamad Manjoor</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
@@ -27935,11 +27935,11 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>1495896</v>
+        <v>1495895</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Mohamad Manjoor</t>
+          <t>O P Sharma</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -27972,7 +27972,7 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>Mohamad Manjoor</t>
+          <t>O P Sharma</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
@@ -41708,11 +41708,11 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D666" t="n">
-        <v>16243</v>
+        <v>16525</v>
       </c>
       <c r="E666" t="n">
         <v>525</v>
@@ -53612,11 +53612,11 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D858" t="n">
-        <v>16243</v>
+        <v>16525</v>
       </c>
       <c r="E858" t="n">
         <v>2198</v>
